--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486689_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486689_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5768</v>
+        <v>2.6085</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2278</v>
+        <v>2.2347</v>
       </c>
       <c r="F2" t="n">
-        <v>0.349</v>
+        <v>0.3738</v>
       </c>
       <c r="G2" t="n">
         <v>1.716</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2925</v>
+        <v>0.3242</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0004</v>
+        <v>0.0066</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2928</v>
+        <v>0.3177</v>
       </c>
       <c r="V2" t="n">
         <v>1.1475</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5352</v>
+        <v>2.0096</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0174</v>
+        <v>0.5414</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5179</v>
+        <v>1.4682</v>
       </c>
       <c r="G3" t="n">
         <v>0.4826</v>
@@ -688,13 +688,13 @@
         <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0053</v>
+        <v>0.469</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6622</v>
+        <v>-0.1381</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="V3" t="n">
         <v>0.2856</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9474</v>
+        <v>0.9432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8119</v>
+        <v>1.0809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1355</v>
+        <v>-0.1377</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3689</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5629</v>
+        <v>0.5587</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0004</v>
+        <v>0.2686</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5633</v>
+        <v>0.2901</v>
       </c>
       <c r="V4" t="n">
         <v>1.7188</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2967</v>
+        <v>-0.3237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0271</v>
+        <v>-1.2538</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3238</v>
+        <v>0.9301</v>
       </c>
       <c r="G5" t="n">
-        <v>0.102</v>
+        <v>1.7172</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1307</v>
+        <v>4.717</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0286</v>
+        <v>-2.9999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9651999999999999</v>
+        <v>2.0286</v>
       </c>
       <c r="K5" t="n">
-        <v>1.614</v>
+        <v>4.0971</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6488</v>
+        <v>-2.0684</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8632</v>
+        <v>-0.3115</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4833</v>
+        <v>0.62</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3799</v>
+        <v>-0.9314</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-4.0546</v>
       </c>
       <c r="R5" t="n">
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.2415</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2204</v>
+        <v>0.1584</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4031</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0222</v>
+        <v>0.6138</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9413</v>
+        <v>-0.4373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3242</v>
+        <v>-0.0142</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2655</v>
+        <v>-0.4232</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5245</v>
+        <v>0.102</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4205</v>
+        <v>1.1307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.945</v>
+        <v>-1.0286</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0761</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0761</v>
+        <v>1.614</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6488</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6006</v>
+        <v>-0.8632</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3443</v>
+        <v>-0.4833</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.945</v>
+        <v>-0.3799</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0386</v>
+        <v>0.4829</v>
       </c>
       <c r="T6" t="n">
-        <v>0.248</v>
+        <v>0.1791</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2095</v>
+        <v>0.3038</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2277</v>
+        <v>-1.0222</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-1.0222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0008</v>
+        <v>-1.0488</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8813</v>
+        <v>0.1173</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8804999999999999</v>
+        <v>-1.1661</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7172</v>
+        <v>-0.5245</v>
       </c>
       <c r="H7" t="n">
-        <v>4.717</v>
+        <v>0.4205</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9999</v>
+        <v>-0.945</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0286</v>
+        <v>0.0761</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0971</v>
+        <v>0.0761</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0684</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3115</v>
+        <v>-0.6006</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.3443</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9314</v>
+        <v>-0.945</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0546</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4356</v>
+        <v>-0.0689</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4691</v>
+        <v>0.0412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0335</v>
+        <v>-0.1101</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6138</v>
+        <v>-1.2277</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0053</v>
+        <v>-2.2277</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9079</v>
+        <v>-0.4554</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0974</v>
+        <v>-1.7722</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.662</v>
+        <v>-2.146</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0471</v>
+        <v>2.303</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.615</v>
+        <v>-4.449</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6976</v>
+        <v>-0.2068</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4361</v>
+        <v>1.8209</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2615</v>
+        <v>-2.0277</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3596</v>
+        <v>-1.9391</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4832</v>
+        <v>0.4821</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8764</v>
+        <v>-2.4212</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2742</v>
+        <v>-0.4689</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8547</v>
+        <v>-0.2486</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4196</v>
+        <v>-0.2203</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4936</v>
+        <v>-1.3505</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1228</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5312</v>
+        <v>-2.7486</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-1.5766</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0205</v>
+        <v>-1.1719</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.146</v>
+        <v>-0.662</v>
       </c>
       <c r="H9" t="n">
-        <v>2.303</v>
+        <v>-0.0471</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.449</v>
+        <v>-0.615</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2068</v>
+        <v>1.6976</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8209</v>
+        <v>0.4361</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0277</v>
+        <v>1.2615</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9391</v>
+        <v>-2.3596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4821</v>
+        <v>-0.4832</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4212</v>
+        <v>-1.8764</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7377</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7724</v>
+        <v>0.531</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3038</v>
+        <v>0.1859</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4686</v>
+        <v>0.3451</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3505</v>
+        <v>-0.4936</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3505</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5054</v>
+        <v>-3.9869</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0482</v>
+        <v>-0.5793</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4572</v>
+        <v>-3.4076</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9452</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4909</v>
+        <v>0.0276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4415</v>
+        <v>0.0274</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0495</v>
+        <v>0.0002</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4931</v>
+        <v>-6.6751</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5645</v>
+        <v>-5.7713</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9286</v>
+        <v>-0.9038</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1996</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5681</v>
+        <v>0.3861</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4136</v>
+        <v>0.2067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1546</v>
+        <v>0.1794</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.7144</v>
+        <v>-11.8868</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5041</v>
+        <v>-5.6763</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.210100000000001</v>
+        <v>-6.2104</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8284</v>
@@ -1360,7 +1360,7 @@
         <v>14.1386</v>
       </c>
       <c r="I12" t="n">
-        <v>-18.96720000000001</v>
+        <v>-18.9672</v>
       </c>
       <c r="J12" t="n">
         <v>5.836499999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-10.665</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.005500000000000171</v>
+        <v>-0.00550000000000006</v>
       </c>
       <c r="O12" t="n">
         <v>-10.6596</v>
@@ -1390,13 +1390,13 @@
         <v>9.654000000000002</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6556</v>
+        <v>2.4832</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1407</v>
+        <v>0.6872</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7961</v>
+        <v>1.7962</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7837</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8584</v>
+        <v>5.3296</v>
       </c>
       <c r="E13" t="n">
-        <v>4.848</v>
+        <v>5.724</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0104</v>
+        <v>-0.3944</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0131</v>
+        <v>3.5021</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0276</v>
+        <v>0.8479</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0407</v>
+        <v>2.6541</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9792999999999999</v>
+        <v>4.3241</v>
       </c>
       <c r="K13" t="n">
-        <v>1.628</v>
+        <v>2.642</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6488</v>
+        <v>1.6821</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.822</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6557</v>
+        <v>-1.7941</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6895</v>
+        <v>0.972</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>1.583</v>
+        <v>-0.3655</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7649</v>
+        <v>-0.09</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1819</v>
+        <v>-0.2755</v>
       </c>
       <c r="V13" t="n">
-        <v>3.0692</v>
+        <v>1.2277</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0692</v>
+        <v>2.4554</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.327</v>
+        <v>3.6959</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2069</v>
+        <v>3.7103</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.88</v>
+        <v>-0.0144</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5021</v>
+        <v>0.0131</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8479</v>
+        <v>-0.0276</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6541</v>
+        <v>0.0407</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3241</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.642</v>
+        <v>1.628</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6821</v>
+        <v>-0.6488</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.822</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7941</v>
+        <v>-1.6557</v>
       </c>
       <c r="O14" t="n">
-        <v>0.972</v>
+        <v>0.6895</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9308</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3682</v>
+        <v>0.4205</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6071</v>
+        <v>0.6272</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.761</v>
+        <v>-0.2067</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2277</v>
+        <v>3.0692</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4554</v>
+        <v>3.0692</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1673</v>
+        <v>3.5865</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.1383</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2358</v>
+        <v>3.4482</v>
       </c>
       <c r="G15" t="n">
         <v>2.4281</v>
@@ -1624,13 +1624,13 @@
         <v>2.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2262</v>
+        <v>0.193</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3866</v>
+        <v>-0.1798</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1604</v>
+        <v>0.3728</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5168</v>
+        <v>1.0424</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0295</v>
+        <v>-0.4432</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5463</v>
+        <v>1.4856</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1684</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9708</v>
+        <v>0.4964</v>
       </c>
       <c r="T16" t="n">
-        <v>0.358</v>
+        <v>-0.0557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6128</v>
+        <v>0.5521</v>
       </c>
       <c r="V16" t="n">
         <v>0.3282</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1911</v>
+        <v>0.6724</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9165</v>
+        <v>-1.3791</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1076</v>
+        <v>2.0515</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7799</v>
+        <v>-1.5756</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.2417</v>
+        <v>-1.0964</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4618</v>
+        <v>-0.4793</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3182</v>
+        <v>-1.8576</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.62</v>
+        <v>-0.6821</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9382</v>
+        <v>-1.1755</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0981</v>
+        <v>0.2819</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6217</v>
+        <v>-0.4143</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5236</v>
+        <v>0.6962</v>
       </c>
       <c r="P17" t="n">
         <v>1.7377</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7031</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7667</v>
+        <v>0.5103</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2693</v>
+        <v>0.1928</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5026</v>
+        <v>0.3175</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1842</v>
+        <v>0.4199</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7928</v>
+        <v>-1.5028</v>
       </c>
       <c r="F18" t="n">
-        <v>1.977</v>
+        <v>1.9227</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5756</v>
+        <v>-0.7799</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0964</v>
+        <v>-3.2417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4793</v>
+        <v>2.4618</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8576</v>
+        <v>0.3182</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6821</v>
+        <v>-0.62</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1755</v>
+        <v>0.9382</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2819</v>
+        <v>-1.0981</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4143</v>
+        <v>-2.6217</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6962</v>
+        <v>1.5236</v>
       </c>
       <c r="P18" t="n">
         <v>1.7377</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0221</v>
+        <v>-0.5379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2208</v>
+        <v>-0.8556</v>
       </c>
       <c r="U18" t="n">
-        <v>0.243</v>
+        <v>0.3177</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0781</v>
+        <v>-0.0365</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7371</v>
+        <v>-0.2084</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.659</v>
+        <v>0.1719</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5155</v>
+        <v>1.067</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0277</v>
+        <v>-1.6345</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5432</v>
+        <v>2.7015</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1372</v>
+        <v>1.2053</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3028</v>
+        <v>-0.6688</v>
       </c>
       <c r="L19" t="n">
-        <v>4.44</v>
+        <v>1.8741</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6217</v>
+        <v>-0.1384</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7249</v>
+        <v>-0.9657</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1032</v>
+        <v>0.8274</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5958</v>
+        <v>-0.2966</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4693</v>
+        <v>-0.4484</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1265</v>
+        <v>0.1518</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8415</v>
+        <v>-0.6138</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8415</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3138</v>
+        <v>-0.1398</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3119</v>
+        <v>0.5302</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0019</v>
+        <v>-0.6701</v>
       </c>
       <c r="G20" t="n">
-        <v>1.067</v>
+        <v>2.5155</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6345</v>
+        <v>-3.0277</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7015</v>
+        <v>5.5432</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2053</v>
+        <v>3.1372</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6688</v>
+        <v>-1.3028</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8741</v>
+        <v>4.44</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1384</v>
+        <v>-0.6217</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9657</v>
+        <v>-1.7249</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8274</v>
+        <v>1.1032</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5738</v>
+        <v>-0.8138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5518</v>
+        <v>-0.6762</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.022</v>
+        <v>-0.1376</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6138</v>
+        <v>-1.8415</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6138</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2947</v>
+        <v>-1.1664</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4624</v>
+        <v>-0.359</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8074</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1732</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7007</v>
+        <v>-0.5724</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4139</v>
+        <v>-0.3105</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2868</v>
+        <v>-0.2619</v>
       </c>
       <c r="V21" t="n">
         <v>0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>12.7144</v>
+        <v>13.404</v>
       </c>
       <c r="E22" t="n">
-        <v>6.210299999999999</v>
+        <v>6.2103</v>
       </c>
       <c r="F22" t="n">
-        <v>6.504</v>
+        <v>7.193599999999999</v>
       </c>
       <c r="G22" t="n">
         <v>4.8287</v>
@@ -2170,13 +2170,13 @@
         <v>16.4117</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6555</v>
+        <v>-0.966</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7959</v>
+        <v>-1.7962</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1406</v>
+        <v>0.8302</v>
       </c>
       <c r="V22" t="n">
         <v>2.7836</v>
